--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/03_BIBS_Signoff_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/03_BIBS_Signoff_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -27,7 +27,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_lists" sheetId="18" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$141</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'How to review'!$A$4:$B$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'How to review'!$4:$4</definedName>
@@ -57,7 +57,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'Meeting minutes'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Version history'!$A$4:$E$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="15">'Version history'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Sign-off certificate'!$A$4:$H$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Sign-off certificate'!$A$4:$J$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="16">'Sign-off certificate'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -25934,17 +25934,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -25970,44 +25972,56 @@
       <c r="F3" s="23" t="n"/>
       <c r="G3" s="23" t="n"/>
       <c r="H3" s="23" t="n"/>
+      <c r="I3" s="23" t="n"/>
+      <c r="J3" s="23" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Signs for</t>
-        </is>
-      </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
+          <t>Confirms</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>On the BRD approval sheet</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Signature</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -26016,194 +26030,402 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Product Owner, Marketing Business System</t>
+          <t>Prepared by</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>BDOI</t>
+          <t>iorta TechNXT project team: Project Manager, Business Analysis, test lead</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Business owner: the whole set</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
+          <t>iorta TechNXT</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>The set is complete and consistent as issued, traced to the BRD and to the screens; every comment is answered in the comments log</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Added for this set (author of the FRS set)</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="25" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Head, Marketing Business Services and System Support</t>
+          <t>Prepared by</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>BDOI</t>
+          <t>Business Analyst, Enterprise Services Group - Business Project Services (BPS)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Set-up, versions, masters, incentive criteria and the configuration inputs</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
+          <t>BDO Unibank ESG</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>The set states the BRD requirements as written; every departure is listed in the proposed rules and clarifications</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Prepared by (p.34, p.8)</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
-      <c r="H6" s="25" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="25" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Head, Technical Support Unit</t>
+          <t>Input provided by</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
+          <t>Technical Support Unit (TSU), BU representatives</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
           <t>BDOI</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Package requests, negotiation, requirements, advisories and expiry</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>The package request, negotiation, requirements, advisory and expiry screens match the business input</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Input provided by (p.34, p.8)</t>
+        </is>
+      </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
-      <c r="H7" s="25" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="25" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Head, Retail Marketing</t>
+          <t>Input provided by</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
+          <t>Marketing Business System (MBS), BU representatives</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
           <t>BDOI</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Package requests, approvals and pricing screens</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>The set-up, version, master and incentive screens and the configuration inputs match the business input</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Input provided by and Reviewed by (p.34, p.8)</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
-      <c r="H8" s="25" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="25" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Head, Comptrollership</t>
+          <t>Reviewed by</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>BDOI</t>
+          <t>Program Manager, Enterprise Services Group - Business Project Services (BPS)</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Finance: rates and taxes, commission rates, incentive criteria</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
+          <t>BDO Unibank ESG</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Traceability of every BRD requirement to the set and completeness of the set</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Reviewed by (p.34, p.9)</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
-      <c r="H9" s="25" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="25" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Head, BDOI IT</t>
+          <t>Reviewed by</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
+          <t>BDOI Information Technology Group (BDOI IT)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
           <t>BDOI</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>BDOI IT: interfaces, user access and menus</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Interfaces, user access and menus, and the Technical Specification (a separate document); not the business screens</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Added for this set</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
-      <c r="H10" s="25" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="25" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Program Manager, Business Project Services</t>
+          <t>Approved by</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>BDO Unibank ESG</t>
+          <t>Product Owner, Marketing Business System</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Traceability to the BRD</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
+          <t>BDOI</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Owns the set and approves all of its contents</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Approved by (p.34, p.9)</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
-      <c r="H11" s="25" t="n"/>
+      <c r="H11" s="12" t="n"/>
+      <c r="I11" s="12" t="n"/>
+      <c r="J11" s="25" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Approved by</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>iorta TechNXT</t>
+          <t>Unit Head - Claims, Analytics, Risk Management, Reinsurance and Technical Underwriting</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Delivery of the set as signed</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
+          <t>BDOI</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>The TSU part: package requests, negotiation, requirements, advisories and expiry</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Approved by (p.35, p.9)</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
-      <c r="H12" s="25" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="25" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Unit Head - Combank and Corbank</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>BDOI</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Package requests, approvals and pricing for Combank and Corbank</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Approved by (p.35, p.9)</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="25" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Head - Retail Marketing</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>BDOI</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Package requests, approvals and pricing for Retail Marketing</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Approved by (p.35, p.9)</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="25" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Head - Corporate and Retail Marketing</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>BDOI</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Package requests, approvals and pricing for Corporate Marketing</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Approved by (p.35)</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="12" t="n"/>
+      <c r="I15" s="12" t="n"/>
+      <c r="J15" s="25" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Head - Comptrollership</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>BDOI</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Rates and taxes, commission rates and incentive criteria</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Approved by (p.35; marked not required on the addendum, p.9)</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="25" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H12"/>
+  <autoFilter ref="A4:J16"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H512">
+  <conditionalFormatting sqref="A5:J516">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E5:E512" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Decision" error="Choose a value from the list (Decision)." type="list">
+    <dataValidation sqref="G5:G516" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Decision" error="Choose a value from the list (Decision)." type="list">
       <formula1>'_lists'!$I$1:$I$3</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Review date" error="Enter a date (dd-mmm-yyyy)." type="date" operator="greaterThan">
+    <dataValidation sqref="J5:J5000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Review date" error="Enter a date (dd-mmm-yyyy)." type="date" operator="greaterThan">
       <formula1>DATE(2026,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -26396,7 +26618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -28767,12 +28989,12 @@
       </c>
       <c r="B132" s="21" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Signatory role</t>
+          <t>Prepared by, Input provided by, Reviewed by or Approved by, as on the BRD approval sheet</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr"/>
@@ -28785,12 +29007,12 @@
       </c>
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Signatory role</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr"/>
@@ -28803,12 +29025,12 @@
       </c>
       <c r="B134" s="21" t="inlineStr">
         <is>
-          <t>Signs for</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Part of the set the signatory confirms</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr"/>
@@ -28821,12 +29043,12 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Confirms</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Name of the signatory</t>
+          <t>What the signatory confirms by signing</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr"/>
@@ -28839,19 +29061,15 @@
       </c>
       <c r="B136" s="21" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>On the BRD approval sheet</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Approved, Approved with comments or Not approved</t>
-        </is>
-      </c>
-      <c r="D136" s="14" t="inlineStr">
-        <is>
-          <t>Approved, Approved with comments, Not approved</t>
-        </is>
-      </c>
+          <t>Where the role signs the BRD (BRD-3 approval sheets: main BRD p.34-35; Workshop Addendum p.8-9)</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="inlineStr">
@@ -28861,12 +29079,12 @@
       </c>
       <c r="B137" s="20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Conditions of the approval</t>
+          <t>Name of the signatory</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr"/>
@@ -28879,15 +29097,19 @@
       </c>
       <c r="B138" s="21" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="D138" s="14" t="inlineStr"/>
+          <t>Approved, Approved with comments or Not approved</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Approved, Approved with comments, Not approved</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
@@ -28897,18 +29119,54 @@
       </c>
       <c r="B139" s="20" t="inlineStr">
         <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>Conditions of the approval</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="inlineStr">
+        <is>
+          <t>Sign-off certificate</t>
+        </is>
+      </c>
+      <c r="B140" s="21" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>Sign-off certificate</t>
+        </is>
+      </c>
+      <c r="B141" s="20" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C139" s="12" t="inlineStr">
+      <c r="C141" s="12" t="inlineStr">
         <is>
           <t>Date of the decision</t>
         </is>
       </c>
-      <c r="D139" s="12" t="inlineStr"/>
+      <c r="D141" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D139"/>
+  <autoFilter ref="A4:D141"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -48387,7 +48645,7 @@
       </c>
       <c r="L244" s="12" t="inlineStr">
         <is>
-          <t>Valid JSON</t>
+          <t>Name and value pairs as in the example</t>
         </is>
       </c>
       <c r="M244" s="12" t="inlineStr">
@@ -68203,7 +68461,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>Enter the rule parameters as valid JSON, for example {"minimumPremium": 5000}.</t>
+          <t>Enter the rule parameters as name and value pairs in braces, as in the example {"minimumPremium": 5000}.</t>
         </is>
       </c>
       <c r="H197" s="12" t="n"/>

--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/03_BIBS_Signoff_BRD-03_Product_Maintenance_v2.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/BRD-03_Product_Maintenance/03_BIBS_Signoff_BRD-03_Product_Maintenance_v2.0.xlsx
@@ -29940,7 +29940,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>A package request shows the workflow header under the record header: a stepper of the stages of the request in their order (passed stages ticked in blue, the current stage highlighted, the stages ahead in grey with their number; a returned stage in amber, a voided or not proceeded request in red, Released in green once reached), and under it one row with Current Stage, Since, Due (the service level due time, with the Overdue pill) and Assigned To (the user's name), with the actions the user may take now on the right. The History tab lists every step, newest first: Stage, From Stage, Action, By (name and role), Date and Time, Remarks and Duration in Stage. Actions that need a reason (Return to requester, Void, Not proceeded, Request changes, Return to TSU) open a dialog with the mandatory reason from its list of values and an optional comment; the comment is kept in the history and sent with the workflow notice.</t>
+          <t>A package request shows the workflow header under the record header: a stepper of the stages of the request in their order (passed stages ticked in blue, the current stage highlighted, the stages ahead in grey with their number; a returned stage in amber, a voided or not proceeded request in red, Released in green once reached), and under it one row with Current Stage, Since, Due (the service level due time, with the Overdue pill) and Assigned To (the user's name), with the actions the user may take now on the right. The History tab lists every step, newest first: Stage, From Stage, Action, By (the user's name; the role under it for the users who may read the roles of others: user administration, access review and audit), Date and Time, Remarks and Duration in Stage. Actions that need a reason (Return to requester, Void, Not proceeded, Request changes, Return to TSU) open a dialog with the mandatory reason from its list of values and an optional comment; the comment is kept in the history and sent with the workflow notice.</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
